--- a/Guia_Diagrama_de_Gantt.xlsx
+++ b/Guia_Diagrama_de_Gantt.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I30"/>
+  <dimension ref="B1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Este libro de Gantt fue ampliado SIN modificar ningún dato, fecha, nombre, estado ni fórmula existente. Todas las mejoras son aditivas (formato condicional, hojas auxiliares y fórmulas).</t>
+          <t>Libro ampliado SIN modificar ningún dato, fecha, nombre, estado ni fórmula existente. Todo es aditivo (formato condicional, hojas auxiliares y fórmulas). La hoja Gantt original solo recibió formato condicional.</t>
         </is>
       </c>
     </row>
@@ -503,126 +503,126 @@
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>• Proyecto Datos (OKR´s): es la hoja Gantt original. Se le agregó SOLO formato condicional: semáforo de vencimiento en la columna F y escala de color por sprint en la columna E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>• Proyecto Datos (OKR´s): Gantt original. Se agregó solo formato condicional: semáforo de vencimiento (col F), escala de color por sprint (col E) y barras del Gantt extendidas a filas nuevas (56-200).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>• Tablero: resumen ejecutivo (KPIs, avance por módulo OKR y avance por sprint). Aquí está el resumen por sprint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+          <t>• Tablero: KPIs, avance por módulo OKR, avance por sprint (vigente) y panel de Alertas/Cuellos de botella.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>• Entregas Próximas: lista automática de entregas, ordenada por sprint y luego por fecha (columna F), con semáforo de estado. La pantalla está inmovilizada solo en el encabezado para ver muchas filas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+          <t>• Entregas Próximas: lista priorizada de tareas (orden por prioridad) con días estimados/reales, variación, atraso y alertas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>• _Datos (oculta): motor de cálculo. Lee la hoja Gantt y prepara los datos. No editar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>CRITERIOS DE ESTADO (semáforo)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Fecha de entrega = columna F (Fecha) si existe; si está vacía se usa la columna L (FIN) como respaldo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+          <t>• Historial de Sprints: configuración del sprint + registro automático de tareas reasignadas entre sprints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>• _Datos (oculta): motor de cálculo. No editar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1) GESTIÓN DINÁMICA DE TAREAS</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="46" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>• Completado: Progreso ≥ 100%.   • Vencido: fecha de entrega anterior a HOY y progreso &lt; 100%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>• Próximo a vencer: faltan entre 0 y el 'umbral' de días (editable en Entregas Próximas, por defecto 7).   • En curso: dentro de plazo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Colores: Rojo = Vencido · Amarillo = Próximo a vencer · Verde = En curso/Completado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>FÓRMULAS CLAVE</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
+          <t>Para agregar una tarea: escriba en una fila nueva del Gantt (Tarea col G, Inicio col K, y Fecha col F y/o Fin col L). Recomendado: inserte la fila DENTRO de un módulo para que Excel copie las fórmulas. Todo se actualiza solo: barras del Gantt (FC ampliado a fila 200), Tablero, Entregas Próximas e Historial. No hay que tocar fórmulas ni rangos (todos llegan a la fila 200).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2) ESTADOS Y PRIORIZACIÓN (Entregas Próximas)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>FechaObjetivo = col F si existe; si no, col L (FIN). Estado: Completado (Prog≥100%) · Vencido (FechaObj&lt; HOY) · Próximo a vencer (faltan ≤ umbral, editable en M3, def. 7) · En curso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Métricas: Dur.estimada = FinPlan−Inicio+1 · Días reales = HOY−Inicio · Avance esperado = (HOY−Inicio)/(FinPlan−Inicio) · Variación = Progreso − Avance esperado (negativo = atraso) · Atraso(d) = HOY−FechaObjetivo · Desvío plan = FinPlan − FechaObjetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>• Ordenamiento sin macros: SMALL + MATCH + INDEX sobre una 'ClaveOrden' = Sprint×1.000.000 + Fecha + Fila/100.000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+          <t>Score de prioridad (0-100) = 35%·Urgencia + 30%·Atraso + 20%·Riesgo + 15%·Carga. Clasificación: ≥70 Crítica · ≥45 Alta · ≥25 Media · resto Baja. Urgencia por días restantes; Atraso por variación/atraso; Riesgo por bloqueo y bajo avance cerca del plazo; Carga por nº de tareas pendientes del responsable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>• Tareas vs. fases: las filas de fase tienen TEXTO en la columna INICIO (K); las tareas tienen una FECHA. EsTarea = Y(hay tarea; no es fase; hay fecha).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>• Módulo de cada tarea: LOOKUP(2;1/(...)) localiza el último título de fase situado por encima.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>• Sprints dinámicos: la lista de sprints (Tablero) muestra SOLO los que existen; aparecen automáticamente al usarse y el histórico se conserva. '(Sin sprint)' agrupa las tareas sin número.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
+          <t>Cuellos de botella (col Alerta): ATRASO (variación&lt;−20% o atraso&gt;0) · BLOQUEO (debía iniciar y sigue en 0%) · SOBRECARGA (responsable con &gt;8 pendientes) · DESVÍO-PLAN (FIN supera la fecha objetivo). Nota: el modelo no tiene columna de dependencias, por eso el bloqueo se infiere del inicio vencido sin avance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>3) AUTOMATIZACIÓN DE SPRINT (sin intervención manual)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>• Métricas: COUNTIF/COUNTIFS, MINIFS y AVERAGEIF sobre rangos amplios (filas 7 a 200).</t>
+          <t>En 'Historial de Sprints' se define Inicio Sprint 1 y Duración (editables). Sprint actual = ENTERO((HOY−Inicio)/Duración)+1. Regla: si una tarea NO está 'Completada' y su sprint ya cerró, su 'Sprint vigente' = sprint actual (se reasigna automáticamente al siguiente). El Sprint planificado original (col E del Gantt) NO se toca: queda como histórico. Todo es por fórmula, se recalcula solo al abrir/cambiar fechas.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ESCALABILIDAD</t>
+          <t>4) TRAZABILIDAD (Historial de Sprints)</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -633,74 +633,104 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Todas las fórmulas abarcan hasta la fila 200 de la hoja Gantt. Se pueden agregar sprints, tareas, entregables, responsables y fechas: el Tablero y Entregas Próximas se actualizan solos. Para superar 200 filas, amplíe el rango en la hoja _Datos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES DETECTADAS (no se modificaron datos; se informan para revisión)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="46" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>• Promedios de fase: las celdas J27 y J36 (fases 4 y 5) promedian rangos que no corresponden a sus tareas (muestran 38% y 17% cuando el avance real es 72% y 43%). El Tablero ya recalcula el avance por módulo de forma correcta. Para corregir el origen: J27 → =PROMEDIO(J28:J35) ; J36 → =PROMEDIO(J37:J47).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
+          <t>Registra cada reasignación: ID de tarea, Tarea, Responsable, Sprint origen, Sprint destino, Fecha del movimiento (cierre del sprint origen) y Motivo. Se completa automáticamente con las tareas cuyo Sprint vigente ≠ Sprint planificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Para un registro PERSISTENTE con write-back físico + usuario de Windows, use la macro opcional 'macro_sprints.bas' (ver README): reasigna el nº de sprint en el Gantt y agrega una línea con fecha/usuario. Requiere guardar como .xlsm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ESCALABILIDAD</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>• Fechas a revisar (posibles errores de carga, no modificadas): K13 = 19/11/2026 (posterior a su FIN), K40 = 01/12/2026 y filas con INICIO mayor que FIN (41, 42, 46, 47), que generan DÍAS negativos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>• Filas 79-80 contienen textos sueltos sin fecha; quedan excluidos de los cálculos automáticamente.</t>
+          <t>Las fórmulas llegan a la fila 200 del Gantt. Para superar 200 filas, amplíe el rango en _Datos. Los sprints aparecen solos al usarse (lista dinámica) y conservan el histórico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES (no se modificaron datos; se informan para revisión)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>• Promedios de fase J27 y J36: promedian rangos que no corresponden (38% y 17% cuando el real es 72% y 43%). El Tablero ya lo recalcula bien. Para corregir el origen: J27 → =PROMEDIO(J28:J35) ; J36 → =PROMEDIO(J37:J47).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>• Fechas a revisar: K13 (19/11/2026, posterior al FIN), K40 (01/12/2026) y filas con INICIO &gt; FIN (41,42,46,47) → días negativos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>• Filas 79-80: textos sueltos sin fecha; se excluyen automáticamente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B16:I16"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B14:I14"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B10:I10"/>
     <mergeCell ref="B28:I28"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B20:I20"/>
     <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Guia_Diagrama_de_Gantt.xlsx
+++ b/Guia_Diagrama_de_Gantt.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I34"/>
+  <dimension ref="B1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -612,122 +612,130 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
     </row>
-    <row r="22" ht="50" customHeight="1">
+    <row r="22" ht="46" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>En 'Historial de Sprints' se define Inicio Sprint 1 y Duración (editables). Sprint actual = ENTERO((HOY−Inicio)/Duración)+1. Regla: si una tarea NO está 'Completada' y su sprint ya cerró, su 'Sprint vigente' = sprint actual (se reasigna automáticamente al siguiente). El Sprint planificado original (col E del Gantt) NO se toca: queda como histórico. Todo es por fórmula, se recalcula solo al abrir/cambiar fechas.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Postergar manual por cuello de botella (hoja 'Postergar'): en la fila de la tarea elija 'Postergar (nº sprints)' (lista 0-3; 1 = próximo) y el 'Motivo' (lista editable: dependencia, sobrecarga, falta de info, reestimación, recurso, prioridad, bloqueo técnico, otro). El Sprint vigente se ajusta solo y el movimiento queda registrado con ese motivo. Botón opcional de 1 clic: macro 'PostergarTareaActual' (archivo macro_sprints.bas) — asígnela a un botón de formulario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>4) TRAZABILIDAD (Historial de Sprints)</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Registra cada reasignación: ID de tarea, Tarea, Responsable, Sprint origen, Sprint destino, Fecha del movimiento (cierre del sprint origen) y Motivo. Se completa automáticamente con las tareas cuyo Sprint vigente ≠ Sprint planificado.</t>
-        </is>
-      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>Registra cada reasignación: ID de tarea, Tarea, Responsable, Sprint origen, Sprint destino, Fecha del movimiento (cierre del sprint origen) y Motivo. Se completa automáticamente con las tareas cuyo Sprint vigente ≠ Sprint planificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>Para un registro PERSISTENTE con write-back físico + usuario de Windows, use la macro opcional 'macro_sprints.bas' (ver README): reasigna el nº de sprint en el Gantt y agrega una línea con fecha/usuario. Requiere guardar como .xlsm.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>ESCALABILIDAD</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Las fórmulas llegan a la fila 200 del Gantt. Para superar 200 filas, amplíe el rango en _Datos. Los sprints aparecen solos al usarse (lista dinámica) y conservan el histórico.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES (no se modificaron datos; se informan para revisión)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>• Promedios de fase J27 y J36: promedian rangos que no corresponden (38% y 17% cuando el real es 72% y 43%). El Tablero ya lo recalcula bien. Para corregir el origen: J27 → =PROMEDIO(J28:J35) ; J36 → =PROMEDIO(J37:J47).</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>• Fechas a revisar: K13 (19/11/2026, posterior al FIN), K40 (01/12/2026) y filas con INICIO &gt; FIN (41,42,46,47) → días negativos.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>• Filas 79-80: textos sueltos sin fecha; se excluyen automáticamente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B25:I25"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B27:I27"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B23:I23"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B28:I28"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B30:I30"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B32:I32"/>
     <mergeCell ref="B26:I26"/>

--- a/Guia_Diagrama_de_Gantt.xlsx
+++ b/Guia_Diagrama_de_Gantt.xlsx
@@ -524,7 +524,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>• Historial de Sprints: configuración del sprint + registro automático de tareas reasignadas entre sprints.</t>
+          <t>• Sprints: calendario de reuniones (editable) + seguimiento por tarea (Sprint planificado, vigente, desvío y motivo editable).</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
     <row r="13" ht="46" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Para agregar una tarea: escriba en una fila nueva del Gantt (Tarea col G, Inicio col K, y Fecha col F y/o Fin col L). Recomendado: inserte la fila DENTRO de un módulo para que Excel copie las fórmulas. Todo se actualiza solo: barras del Gantt (FC ampliado a fila 200), Tablero, Entregas Próximas e Historial. No hay que tocar fórmulas ni rangos (todos llegan a la fila 200).</t>
+          <t>Para agregar una tarea: escriba en una fila nueva del Gantt (Tarea col G, Inicio col K, y Fecha col F y/o Fin col L). Recomendado: inserte la fila DENTRO de un módulo para que Excel copie las fórmulas. Todo se actualiza solo: barras del Gantt (FC ampliado a fila 200), Tablero, Entregas Próximas y Sprints. No hay que tocar fórmulas ni rangos (todos llegan a la fila 200).</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3) AUTOMATIZACIÓN DE SPRINT (sin intervención manual)</t>
+          <t>3) SPRINTS POR REUNIÓN (concepto del adjunto)</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -612,45 +612,45 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
     </row>
-    <row r="22" ht="46" customHeight="1">
+    <row r="22" ht="40" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>En 'Historial de Sprints' se define Inicio Sprint 1 y Duración (editables). Sprint actual = ENTERO((HOY−Inicio)/Duración)+1. Regla: si una tarea NO está 'Completada' y su sprint ya cerró, su 'Sprint vigente' = sprint actual (se reasigna automáticamente al siguiente). El Sprint planificado original (col E del Gantt) NO se toca: queda como histórico. Todo es por fórmula, se recalcula solo al abrir/cambiar fechas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
+          <t>Un sprint NO es una tarea: es un PERÍODO de tiempo que cierra en una reunión. En la hoja 'Sprints' hay un CALENDARIO editable (Sprint 1, 2, 3... con su fecha de cierre = la reunión). 'Sprint actual' se calcula solo: es el primer sprint cuya reunión todavía no pasó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Postergar manual por cuello de botella (hoja 'Postergar'): en la fila de la tarea elija 'Postergar (nº sprints)' (lista 0-3; 1 = próximo) y el 'Motivo' (lista editable: dependencia, sobrecarga, falta de info, reestimación, recurso, prioridad, bloqueo técnico, otro). El Sprint vigente se ajusta solo y el movimiento queda registrado con ese motivo. Botón opcional de 1 clic: macro 'PostergarTareaActual' (archivo macro_sprints.bas) — asígnela a un botón de formulario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>4) TRAZABILIDAD (Historial de Sprints)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Registra cada reasignación: ID de tarea, Tarea, Responsable, Sprint origen, Sprint destino, Fecha del movimiento (cierre del sprint origen) y Motivo. Se completa automáticamente con las tareas cuyo Sprint vigente ≠ Sprint planificado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
+          <t>Regla (igual que Scrum): al cerrar la reunión de un sprint, las tareas 'Completadas' quedan registradas en ese sprint; las NO completadas pasan automáticamente al sprint siguiente (Sprint vigente), mostrando el DESVÍO en días. El Sprint planificado (col E del Gantt) NO se toca: es el histórico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Indicar el motivo (cuello de botella): en 'Sprints', columna 'Motivo del desvío', elija de la lista editable (dependencia, sobrecarga, falta de info, reestimación, recurso, prioridad, bloqueo técnico, otro). Es lo único que hay que completar. Botón opcional de 1 clic: macro 'IndicarMotivo' (macro_sprints.bas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>4) TRAZABILIDAD (hoja Sprints)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Para un registro PERSISTENTE con write-back físico + usuario de Windows, use la macro opcional 'macro_sprints.bas' (ver README): reasigna el nº de sprint en el Gantt y agrega una línea con fecha/usuario. Requiere guardar como .xlsm.</t>
+          <t>La tabla 'Seguimiento de tareas por sprint' muestra, por tarea: Sprint planificado → Sprint vigente, el desvío en días y el motivo. Las tareas movidas se resaltan. Para una bitácora PERSISTENTE con fecha/hora y usuario, use la macro opcional 'ReasignarSprintsFisico' (.xlsm) que además reasigna el nº de sprint en el Gantt.</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Las fórmulas llegan a la fila 200 del Gantt. Para superar 200 filas, amplíe el rango en _Datos. Los sprints aparecen solos al usarse (lista dinámica) y conservan el histórico.</t>
+          <t>Las fórmulas llegan a la fila 200 del Gantt. Para superar 200 filas, amplíe el rango en _Datos. El calendario admite hasta 8 sprints (ampliable). Los sprints aparecen solos al usarse y conservan el histórico.</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,6 @@
   </sheetData>
   <mergeCells count="27">
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B25:I25"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B22:I22"/>
@@ -736,6 +735,7 @@
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B32:I32"/>
     <mergeCell ref="B26:I26"/>

--- a/Guia_Diagrama_de_Gantt.xlsx
+++ b/Guia_Diagrama_de_Gantt.xlsx
@@ -615,28 +615,28 @@
     <row r="22" ht="40" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Un sprint NO es una tarea: es un PERÍODO de tiempo que cierra en una reunión. En la hoja 'Sprints' hay un CALENDARIO editable (Sprint 1, 2, 3... con su fecha de cierre = la reunión). 'Sprint actual' se calcula solo: es el primer sprint cuya reunión todavía no pasó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
+          <t>Un sprint NO es una tarea: es un PERÍODO de tiempo que cierra en una REUNIÓN. En la hoja 'Sprints' hay un CALENDARIO editable (Sprint 1, 2, 3... con la fecha de su reunión de cierre). 'Sprint actual' se calcula solo: es el primer sprint cuya reunión todavía no pasó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Regla (igual que Scrum): al cerrar la reunión de un sprint, las tareas 'Completadas' quedan registradas en ese sprint; las NO completadas pasan automáticamente al sprint siguiente (Sprint vigente), mostrando el DESVÍO en días. El Sprint planificado (col E del Gantt) NO se toca: es el histórico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
+          <t>Regla (igual que Scrum): al cerrar la reunión, las tareas 'Completadas' quedan en su sprint; las NO completadas pasan automáticamente al sprint siguiente (Sprint vigente), mostrando el DESVÍO en días. El Sprint planificado (col E del Gantt) NO se toca: es el histórico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Indicar el motivo (cuello de botella): en 'Sprints', columna 'Motivo del desvío', elija de la lista editable (dependencia, sobrecarga, falta de info, reestimación, recurso, prioridad, bloqueo técnico, otro). Es lo único que hay que completar. Botón opcional de 1 clic: macro 'IndicarMotivo' (macro_sprints.bas).</t>
+          <t>Cómo usar la hoja 'Sprints' (3 pasos): 1) edite la fecha de cierre de cada reunión en el calendario; 2) para pasar una tarea al sprint siguiente, elija 'Sí' en la columna 'Pasar al siguiente'; 3) indique el 'Motivo del desvío' (lista editable) y/o escriba un 'Comentario' libre (texto totalmente personalizable). Las filas de cada módulo se agrupan con un encabezado.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>4) TRAZABILIDAD (hoja Sprints)</t>
+          <t>4) TRAZABILIDAD Y MOTIVOS (hoja Sprints)</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -647,10 +647,10 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="46" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>La tabla 'Seguimiento de tareas por sprint' muestra, por tarea: Sprint planificado → Sprint vigente, el desvío en días y el motivo. Las tareas movidas se resaltan. Para una bitácora PERSISTENTE con fecha/hora y usuario, use la macro opcional 'ReasignarSprintsFisico' (.xlsm) que además reasigna el nº de sprint en el Gantt.</t>
+          <t>La tabla 'Seguimiento de tareas por sprint' muestra por tarea: Sprint planificado → Sprint vigente, el desvío en días, el Motivo (lista) y el Comentario (libre). Las tareas movidas se resaltan en ámbar. Motivo = validación de datos (lista editable en P5:P12); Comentario = texto libre. Botones opcionales (.xlsm): 'PasarAlSiguiente' e 'IndicarMotivo'; y 'ReasignarSprintsFisico' para write-back físico + bitácora con fecha/usuario.</t>
         </is>
       </c>
     </row>

--- a/Guia_Diagrama_de_Gantt.xlsx
+++ b/Guia_Diagrama_de_Gantt.xlsx
@@ -482,7 +482,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Libro ampliado SIN modificar ningún dato, fecha, nombre, estado ni fórmula existente. Todo es aditivo (formato condicional, hojas auxiliares y fórmulas). La hoja Gantt original solo recibió formato condicional.</t>
+          <t>Libro ampliado respetando los datos existentes. Se agregó el proyecto NUEVO 'Tablero Forecast' (filas 57-60 del Gantt) como solicitud de la semana; el resto de la hoja Gantt no se modificó.</t>
         </is>
       </c>
     </row>
@@ -500,38 +500,38 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>• Proyecto Datos (OKR´s): Gantt original. Se agregó solo formato condicional: semáforo de vencimiento (col F), escala de color por sprint (col E) y barras del Gantt extendidas a filas nuevas (56-200).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
+          <t>• Backlog General: mis OKRs por proyecto, con sus subtareas. Por cada subtarea se indica Estado (Completo / No se realizó) y, si no se realizó, la Acción (Pasa al siguiente / Baja prioridad / Cancelado) + un Comentario libre. Muestra frecuencia, sprint planificado/vigente, mora y 'Nuevo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>• Tablero: KPIs, avance por módulo OKR, avance por sprint (vigente) y panel de Alertas/Cuellos de botella.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>• Sprints: tres tableros (Semanal / Quincenal / Mensual). Calendario por frecuencia y 'Frecuencia por Proyecto' editables. Cada tarea aparece en el sprint vigente de su frecuencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>• Entregas Próximas: lista priorizada de tareas (orden por prioridad) con días estimados/reales, variación, atraso y alertas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
+          <t>• Tablero: KPIs, avance por módulo OKR, avance por FRECUENCIA y panel de Alertas/Cuellos de botella.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>• Sprints: calendario de reuniones (editable) + seguimiento por tarea (Sprint planificado, vigente, desvío y motivo editable).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+          <t>• Entregas Próximas: lista priorizada (urgencia+atraso+riesgo+carga) con días estimados/reales, variación, atraso y alertas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>• _Datos (oculta): motor de cálculo. No editar.</t>
+          <t>• Proyecto Datos (OKR´s): Gantt original (solo formato condicional + el proyecto nuevo Forecast).  • _Datos (oculta): motor de cálculo, no editar.</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3) SPRINTS POR REUNIÓN (concepto del adjunto)</t>
+          <t>3) SPRINTS POR FRECUENCIA (Semanal / Quincenal / Mensual)</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -615,42 +615,42 @@
     <row r="22" ht="40" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Un sprint NO es una tarea: es un PERÍODO de tiempo que cierra en una REUNIÓN. En la hoja 'Sprints' hay un CALENDARIO editable (Sprint 1, 2, 3... con la fecha de su reunión de cierre). 'Sprint actual' se calcula solo: es el primer sprint cuya reunión todavía no pasó.</t>
+          <t>Cada PROYECTO tiene una frecuencia (editable en Sprints, 'Frecuencia por Proyecto'). Un sprint es un PERÍODO de tiempo: Semanal=7 días, Quincenal=14, Mensual=30 (editable, con su fecha de inicio). El 'Sprint actual' de cada frecuencia se calcula solo. Cada tarea cae en el sprint de su frecuencia según su fecha (Sprint planificado).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Regla (igual que Scrum): al cerrar la reunión, las tareas 'Completadas' quedan en su sprint; las NO completadas pasan automáticamente al sprint siguiente (Sprint vigente), mostrando el DESVÍO en días. El Sprint planificado (col E del Gantt) NO se toca: es el histórico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Cómo usar la hoja 'Sprints' (3 pasos): 1) edite la fecha de cierre de cada reunión en el calendario; 2) para pasar una tarea al sprint siguiente, elija 'Sí' en la columna 'Pasar al siguiente'; 3) indique el 'Motivo del desvío' (lista editable) y/o escriba un 'Comentario' libre (texto totalmente personalizable). Las filas de cada módulo se agrupan con un encabezado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>4) TRAZABILIDAD Y MOTIVOS (hoja Sprints)</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="46" customHeight="1">
+          <t>Regla (igual que Scrum): al cerrar el sprint, las tareas Completadas quedan en su sprint; las NO completadas pasan automáticamente al sprint siguiente (Sprint vigente). Los 3 tableros (Semanal/Quincenal/Mensual) muestran las tareas por sprint con su estado y mora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>4) BACKLOG: COMPLETAR / NO REALIZAR / POSTERGAR</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>En 'Backlog General', por cada subtarea: Estado = 'Completo' o 'No se realizó'. Si NO se realizó, elija la Acción: 'Pasa al siguiente' (va al sprint siguiente y aparece ahí con la misma lógica), 'Baja prioridad' (sigue PENDIENTE pero DEJA de contar días de mora) o 'Cancelado'. El 'Comentario' es texto libre. Las tareas con inicio en la semana actual se marcan 'Nuevo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>La tabla 'Seguimiento de tareas por sprint' muestra por tarea: Sprint planificado → Sprint vigente, el desvío en días, el Motivo (lista) y el Comentario (libre). Las tareas movidas se resaltan en ámbar. Motivo = validación de datos (lista editable en P5:P12); Comentario = texto libre. Botones opcionales (.xlsm): 'PasarAlSiguiente' e 'IndicarMotivo'; y 'ReasignarSprintsFisico' para write-back físico + bitácora con fecha/usuario.</t>
+          <t>El proyecto 'Tablero Forecast' (subtareas: armado de procedimiento; slicer % de incremento sobre venta según factores; factores de clientes con % de incremento) se agregó como solicitud NUEVA de la semana, con la misma clasificación que 'Tablero BI OPEX' (Semanal).</t>
         </is>
       </c>
     </row>
@@ -713,6 +713,7 @@
   </sheetData>
   <mergeCells count="27">
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B25:I25"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B22:I22"/>
@@ -735,7 +736,6 @@
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B32:I32"/>
     <mergeCell ref="B26:I26"/>

--- a/Guia_Diagrama_de_Gantt.xlsx
+++ b/Guia_Diagrama_de_Gantt.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I35"/>
+  <dimension ref="B1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>4) BACKLOG: COMPLETAR / NO REALIZAR / POSTERGAR</t>
+          <t>4) BACKLOG: COMPLETAR / NO REALIZAR + HISTORIAL</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -640,83 +640,91 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
     </row>
-    <row r="26" ht="44" customHeight="1">
+    <row r="26" ht="46" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>En 'Backlog General', por cada subtarea: Estado = 'Completo' o 'No se realizó'. Si NO se realizó, elija la Acción: 'Pasa al siguiente' (va al sprint siguiente y aparece ahí con la misma lógica), 'Baja prioridad' (sigue PENDIENTE pero DEJA de contar días de mora) o 'Cancelado'. El 'Comentario' es texto libre. Las tareas con inicio en la semana actual se marcan 'Nuevo'.</t>
+          <t>En 'Backlog General', por subtarea: Estado = 'Completo' o 'No se realizó'. Si NO se realizó, Acción: 'Pasa al siguiente' (va al sprint siguiente con la misma lógica), 'Baja prioridad' (sigue PENDIENTE pero DEJA de contar días de mora) o 'Cancelado'. Queda el registro de qué no se hizo y por qué: 'Comentario (Gantt)' trae las notas de la 1ª hoja (Gantt) y 'Justificación' es texto libre.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>El proyecto 'Tablero Forecast' (subtareas: armado de procedimiento; slicer % de incremento sobre venta según factores; factores de clientes con % de incremento) se agregó como solicitud NUEVA de la semana, con la misma clasificación que 'Tablero BI OPEX' (Semanal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+          <t>Frecuencia por proyecto: editable por lista (validación de datos) en la hoja Sprints. 'Nuevo': se indica el sprint en que se solicitó (columna 'Sol. en Sprint'); deja de figurar como nuevo al avanzar de sprint (ej.: nuevo en S1 -&gt; ya no en S2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>El proyecto 'Tablero Forecast' (subtareas: armado de procedimiento; slicer % de incremento s/venta según factores; factores de clientes con % de incremento) se agregó DENTRO del bloque de Tableros (25% del OKR), no aparte; el total general sigue siendo 100%. Solicitud nueva de la semana, clasificada como 'Tablero BI OPEX' (Semanal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>ESCALABILIDAD</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Las fórmulas llegan a la fila 200 del Gantt. Para superar 200 filas, amplíe el rango en _Datos. El calendario admite hasta 8 sprints (ampliable). Los sprints aparecen solos al usarse y conservan el histórico.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES (no se modificaron datos; se informan para revisión)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>• Promedios de fase J27 y J36: promedian rangos que no corresponden (38% y 17% cuando el real es 72% y 43%). El Tablero ya lo recalcula bien. Para corregir el origen: J27 → =PROMEDIO(J28:J35) ; J36 → =PROMEDIO(J37:J47).</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>• Fechas a revisar: K13 (19/11/2026, posterior al FIN), K40 (01/12/2026) y filas con INICIO &gt; FIN (41,42,46,47) → días negativos.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>• Filas 79-80: textos sueltos sin fecha; se excluyen automáticamente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B25:I25"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B18:I18"/>
@@ -726,10 +734,9 @@
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B29:I29"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B28:I28"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B30:I30"/>
@@ -737,7 +744,8 @@
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
